--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>65.7756755151397</v>
+        <v>10.6885472712102</v>
       </c>
       <c r="D2" t="n">
-        <v>65.18554938238192</v>
+        <v>10.59265177463706</v>
       </c>
       <c r="E2" t="n">
-        <v>17.04902649789202</v>
+        <v>2.770466805907453</v>
       </c>
       <c r="F2" t="n">
-        <v>13.48091729057701</v>
+        <v>2.190649059718764</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.95456338776751</v>
+        <v>7.792616550512221</v>
       </c>
       <c r="D3" t="n">
-        <v>47.57310872236587</v>
+        <v>7.730630167384454</v>
       </c>
       <c r="E3" t="n">
-        <v>17.04902649789202</v>
+        <v>2.770466805907453</v>
       </c>
       <c r="F3" t="n">
-        <v>13.48091729057701</v>
+        <v>2.190649059718764</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.55766001358585</v>
+        <v>5.940619752207701</v>
       </c>
       <c r="D4" t="n">
-        <v>73.61269393657678</v>
+        <v>11.96206276469373</v>
       </c>
       <c r="E4" t="n">
-        <v>17.04902649789202</v>
+        <v>2.770466805907453</v>
       </c>
       <c r="F4" t="n">
-        <v>13.48091729057701</v>
+        <v>2.190649059718764</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.27610413106506</v>
+        <v>7.519866921298073</v>
       </c>
       <c r="D5" t="n">
-        <v>81.44596868224141</v>
+        <v>13.23496991086423</v>
       </c>
       <c r="E5" t="n">
-        <v>17.04902649789202</v>
+        <v>2.770466805907453</v>
       </c>
       <c r="F5" t="n">
-        <v>13.48091729057701</v>
+        <v>2.190649059718764</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13.63257944125843</v>
+        <v>2.215294159204495</v>
       </c>
       <c r="D6" t="n">
-        <v>85.51416348706876</v>
+        <v>13.89605156664867</v>
       </c>
       <c r="E6" t="n">
-        <v>17.04902649789202</v>
+        <v>2.770466805907453</v>
       </c>
       <c r="F6" t="n">
-        <v>13.48091729057701</v>
+        <v>2.190649059718764</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
